--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -531,7 +531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -688,7 +688,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -909,7 +909,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>شارژر به حالت امن می‌رود</t>
+          <t>در صورت حضور ورودی معتبر، شارژ مطابق گیت‌های سناریوی ۵/۶ مجاز است</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1174,29 +1174,29 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>هر حالت</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>قفل عدم‌توازن + تیک پارامتر ۱۱۷</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>آنی</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>وتوی خروجی سناریوی ۵</t>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>BATTERY</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>تعویض باتری تأییدشده (نبود پیوستهٔ باتری) و ولتاژ ≥ ۲۱۲۰۰ میلی‌ولت</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>۳۰۰۰ میلی‌ثانیه نبود + ۳۰۰۰ میلی‌ثانیهٔ پیوسته</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>استثنای ۲۰۲۶-۱۰-۲۳: بدون برق شهر هم وصل می‌شود</t>
         </is>
       </c>
     </row>
@@ -1213,44 +1213,71 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
+          <t>قفل عدم‌توازن + تیک پارامتر ۱۱۷</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>آنی</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>وتوی خروجی سناریوی ۵</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>هر حالت</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
           <t>حکم باتری خراب + تیک پارامتر ۱۲۷</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>آنی</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>وتوی خروجی سناریوی ۶</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>ورودی قطع است</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>ورودی قطع است و باتری هم جدا نشده</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>بدون ورودی، وصل مجدد انجام نمی‌شود (تصمیم تأییدشدهٔ کاربر)</t>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>بدون ورودی و بدون تعویض باتری، وصل مجدد انجام نمی‌شود (تصمیم ۲۰۲۶-۱۰-۰۶)</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1186,17 +1186,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>تعویض باتری تأییدشده (نبود پیوستهٔ باتری) و ولتاژ ≥ ۲۱۲۰۰ میلی‌ولت</t>
+          <t>ولتاژ سالم و پیوسته ≥ ۲۱۲۰۰ میلی‌ولت بدون برق شهر (بازیابی یا تعویض باتری)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>۳۰۰۰ میلی‌ثانیه نبود + ۳۰۰۰ میلی‌ثانیهٔ پیوسته</t>
+          <t>۱۰۰۰۰ میلی‌ثانیهٔ پیوسته + ۳۰۰۰ میلی‌ثانیه</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>استثنای ۲۰۲۶-۱۰-۲۳: بدون برق شهر هم وصل می‌شود</t>
+          <t>استثنای ۲۰۲۶-۱۰-۲۳، با محافظ چرخهٔ ۶۰ ثانیه</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>ورودی قطع است و باتری هم جدا نشده</t>
+          <t>ورودی قطع است و ولتاژ سالم کمتر از ۱۰ ثانیه پیوسته مانده</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1277,7 +1277,34 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>بدون ورودی و بدون تعویض باتری، وصل مجدد انجام نمی‌شود (تصمیم ۲۰۲۶-۱۰-۰۶)</t>
+          <t>بدون برق شهر و بدون پنجرهٔ سالمِ کامل، وصل انجام نمی‌شود</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>بعد از وصلِ بدون برق شهر، قطع دوباره ظرف ۶۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>محافظ چرخه: تا برگشت برق شهر وصل خودکار انجام نمی‌شود</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -10,6 +10,7 @@
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="۲ گذارها" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="۳ سناریوی ۸ (باتری ضعیف)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,11 +80,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
@@ -105,6 +101,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -145,13 +146,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +160,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -535,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -602,72 +606,89 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>۳ سناریوی ۸ (باتری ضعیف)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>حکم، قفل، بسته‌ماندن خروجی و پاک‌شدن</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>changeover.c، changeover.h</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>فایل‌های مرجع</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Firmware/Modules/Changeover/changeover.c، Firmware/Config/Inc/app_types.h</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>برگهٔ اعتبارسنجی همین ماژول</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Changeover_Board_Validation.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>برگهٔ اعتبارسنجی همین ماژول</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Changeover_Board_Validation.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
@@ -678,8 +699,8 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1314,4 +1335,285 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>حکم باتری ضعیف، قفل، بسته‌ماندن خروجی و پاک‌شدن — شناسه‌های ۱۴۷..۱۵۷</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>گام</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>حالت حکم</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>شرط ورود</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>خروجی (PB11)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>چهرهٔ LED/بوق</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>پارامتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>۱</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>بدون حکم</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>حکم قفل نیست</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>مسیر باتری طبق گذارهای عادی</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>۲</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>وصلِ بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>ولتاژ ≥ ۲۱۲۰۰ mV پیوسته</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>پس از ۳ ثانیه وصل می‌شود</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>۳</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>قطع دوباره</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>قطع داخل پنجرهٔ محافظ بعد از وصلِ بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>قطع می‌ماند</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>۴</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>حکم قفل شد</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>قطعِ گام ۳ و ۱۴۷ ≠ ۰</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>قطع (اگر ۱۵۷ = ۱)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>قرمز چشمک‌زن + بوق مستقل</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>۵</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>حکم برجاست (برق شهر برگشت)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>input_present = true</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>مسیر از راه ورودی باز، حکم پاک نمی‌شود</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>همان چهره با قطع برق شهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>۶</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>استراحت</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>ولتاژ سالم پیوسته ≥ ۲۱۲۰۰ mV</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>قطع می‌ماند</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>همان چهره</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>۷</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>پاک‌شدن و یک تلاش مجدد</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>پایان استراحت، یا ۱۴۷ = ۰</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>یک بار وصل مجدد مجاز</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>چهره خاموش</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>۸</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>بازگشت به گام ۳</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>تلاش مجدد دوباره قطع شود</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>قطع، حکم از نو قفل</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>قرمز چشمک‌زن + بوق</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -1358,7 +1358,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>حکم باتری ضعیف، قفل، بسته‌ماندن خروجی و پاک‌شدن — شناسه‌های ۱۴۷..۱۵۷</t>
+          <t>حکم باتری ضعیف، قفل، بسته‌ماندن خروجی و پاک‌شدن — شناسه‌های ۱۴۷..۱۵۷ و ریست ۲۰۴</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>پایان استراحت، یا ۱۴۷ = ۰</t>
+          <t>پایان استراحت، ۱۴۷ = ۰، یا دکمهٔ «پاک‌کردن حکم» کارت ۸ (شناسهٔ ۲۰۴)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>یک بار وصل مجدد مجاز</t>
+          <t>یک بار وصل مجدد مجاز؛ خود ریست پین را دست نمی‌زند</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">

--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ گذارها" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="۳ سناریوی ۸ (باتری ضعیف)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ گذارها" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۳ سناریوی ۸ (باتری ضعیف)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,7 +56,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -103,11 +103,6 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -135,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -168,9 +163,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -934,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1207,7 +1199,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>ولتاژ سالم و پیوسته ≥ ۲۱۲۰۰ میلی‌ولت بدون برق شهر (بازیابی یا تعویض باتری)</t>
+          <t>استراحت باتری به آستانهٔ ۱۶۵ (پیش‌فرض ۲۵٬۰۰۰ میلی‌ولت) رسیده باشد و ولتاژ سالم پیوسته ≥ ۲۱۲۰۰ بماند</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1217,7 +1209,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>استثنای ۲۰۲۶-۱۰-۲۳، با محافظ چرخهٔ ۶۰ ثانیه</t>
+          <t>v1.90: زیر آستانهٔ استراحت هیچ وصلِ بدون برق شهری انجام نمی‌شود</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1307,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>بعد از وصلِ بدون برق شهر، قطع دوباره ظرف ۶۰ ثانیه</t>
+          <t>استراحت باتری زیر آستانهٔ ۱۶۵ ماند (مثلاً ۲۳ ولت)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1325,7 +1317,61 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>محافظ چرخه: تا برگشت برق شهر وصل خودکار انجام نمی‌شود</t>
+          <t>v1.90: باتری دشارژ حساب می‌شود؛ وصل نمی‌شود و حکمی هم زده نمی‌شود</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>بعد از همان یک وصلِ بدون برق شهر، قطع دوباره ظرف ۶۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>مسیر تا برگشت برق شهر بسته می‌ماند (سقف تلاش = ۱)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>برق ورودی برگشت و ۳۰ ثانیه ثابت ماند</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>۳۰۰۰۰ + ۳۰۰۰ میلی‌ثانیه</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>چهرهٔ شارژ برمی‌گردد؛ حکم سناریوی ۸ در پس‌زمینه می‌ماند</t>
         </is>
       </c>
     </row>
@@ -1344,13 +1390,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1358,7 +1404,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>حکم باتری ضعیف، قفل، بسته‌ماندن خروجی و پاک‌شدن — شناسه‌های ۱۴۷..۱۵۷ و ریست ۲۰۴</t>
+          <t>حکم باتری فرسوده، سقف یک تلاش، آستانهٔ استراحت و پاک‌شدن — شناسه‌های ۱۴۷..۱۵۷ و ۱۶۵ و ریست ۲۰۴</t>
         </is>
       </c>
     </row>
@@ -1395,218 +1441,322 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>۱</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>بدون حکم</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>حکم قفل نیست</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>مسیر باتری طبق گذارهای عادی</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>۱۴۷ = ۱</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>۲</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>وصلِ بدون برق شهر</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>ولتاژ ≥ ۲۱۲۰۰ mV پیوسته</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>پس از ۳ ثانیه وصل می‌شود</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>قطع ولتاژ پایین</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>ولتاژ &lt; ۲۱۰۰۰ mV به‌مدت ۳ ثانیه</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>قطع؛ تا برگشت برق ورودی</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>هر سه چراغ و بوق خاموش</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>۳</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>قطع دوباره</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>قطع داخل پنجرهٔ محافظ بعد از وصلِ بدون برق شهر</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>استراحت پایین (دشارژ)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>استراحت باتری &lt; آستانهٔ ۱۶۵ (مثلاً ۲۳ ولت)</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>قطع می‌ماند؛ هیچ تلاشی نمی‌شود</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>همه خاموش، بدون حکم</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>۱۶۵ (۲۵۰۰۰ mV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>۴</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>استراحت بالا</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>استراحت ≥ ۱۶۵ و ولتاژ سالم پیوسته</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>یک بار بدون برق شهر وصل می‌شود</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>۱۶۵، ۱۵۰</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>۵</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>قطع دوباره داخل ۶۰ ثانیه</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>قطع داخل پنجرهٔ محافظ بعد از همان یک وصل</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>قطع می‌ماند تا برگشت برق شهر</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>۱۴۹ (۶۰۰۰۰ ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>۶</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>حکم قفل شد</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>قطعِ گام ۵ و ۱۴۷ ≠ ۰</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>قطع (اگر ۱۵۷ = ۱)</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>قرمز چشمک‌زن + بوق، فقط بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>۱۵۱..۱۵۶، ۱۵۷</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>۷</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>حکم برجاست (برق شهر برگشت)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>input_present = true</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>مسیر از راه ورودی باز، حکم پاک نمی‌شود</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>چراغ شارژ عادی (چهرهٔ حکم پنهان)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>۱۴۷، ۱۵۷</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>۸</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>استراحت سالم</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>ولتاژ سالم پیوسته ≥ ۲۱۲۰۰ mV</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>قطع می‌ماند</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>بدون برق شهر: همان چهره</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>۱۴۸ (۶۰۰۰۰۰ ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>۹</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>پاک‌شدن و یک تلاش مجدد</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>پایان استراحت، ۱۴۷ = ۰، یا دکمهٔ «پاک‌کردن حکم» کارت ۸ (شناسهٔ ۲۰۴)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>یک بار وصل مجدد مجاز؛ خود ریست پین را دست نمی‌زند</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>چهرهٔ حکم خاموش</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>۱۴۷، ۱۴۸، ۲۰۴</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>۱۰</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>قطع سیم باتری بدون برق شهر</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ولتاژ خوانده‌شده ≈ صفر</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>قطع، سکوت کامل، بدون آلارم</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>همه خاموش</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>۴</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>حکم قفل شد</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>قطعِ گام ۳ و ۱۴۷ ≠ ۰</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>قطع (اگر ۱۵۷ = ۱)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>قرمز چشمک‌زن + بوق مستقل</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>۵</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>حکم برجاست (برق شهر برگشت)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>input_present = true</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>مسیر از راه ورودی باز، حکم پاک نمی‌شود</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>همان چهره با قطع برق شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>۶</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>استراحت</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>ولتاژ سالم پیوسته ≥ ۲۱۲۰۰ mV</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>قطع می‌ماند</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>همان چهره</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>۷</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>پاک‌شدن و یک تلاش مجدد</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>پایان استراحت، ۱۴۷ = ۰، یا دکمهٔ «پاک‌کردن حکم» کارت ۸ (شناسهٔ ۲۰۴)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>یک بار وصل مجدد مجاز؛ خود ریست پین را دست نمی‌زند</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>چهره خاموش</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>۸</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>بازگشت به گام ۳</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>تلاش مجدد دوباره قطع شود</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>قطع، حکم از نو قفل</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>قرمز چشمک‌زن + بوق</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
+++ b/Firmware/Modules/Changeover/Changeover_State_Machine.xlsx
@@ -926,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>۳۰۰۰ میلی‌ثانیهٔ پیوسته</t>
+          <t>۳۰۰۰۰ میلی‌ثانیه پایداری ورودی + ۳۰۰۰ میلی‌ثانیه ولتاژ</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1345,33 +1345,6 @@
       <c r="E16" s="10" t="inlineStr">
         <is>
           <t>مسیر تا برگشت برق شهر بسته می‌ماند (سقف تلاش = ۱)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>INPUT</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>برق ورودی برگشت و ۳۰ ثانیه ثابت ماند</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>۳۰۰۰۰ + ۳۰۰۰ میلی‌ثانیه</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>چهرهٔ شارژ برمی‌گردد؛ حکم سناریوی ۸ در پس‌زمینه می‌ماند</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1682,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>پایان استراحت، ۱۴۷ = ۰، یا دکمهٔ «پاک‌کردن حکم» کارت ۸ (شناسهٔ ۲۰۴)</t>
+          <t>پایان استراحت، ۱۴۷ = ۰، یا دکمهٔ «پاک‌کردن حکم» کارت ۸ (شناسهٔ ۲۰۴)؛ وصل بدون برق شهر هنوز کف استراحت ۱۶۵ را می‌خواهد</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
